--- a/data/gravel/BMC URS 2025.xlsx
+++ b/data/gravel/BMC URS 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D4930B-2602-8642-9D13-A3F4D4F30B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABD95D6-E0EA-B748-8B92-F2B893CDEBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8920" yWindow="3160" windowWidth="19880" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://us.bmc-switzerland.com/cdn/shop/files/bmc-2026-urs-one-gravel-bike-blue-1_1800x1800.jpg?v=1758296461</t>
   </si>
 </sst>
 </file>
@@ -772,6 +775,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/BMC URS 2025.xlsx
+++ b/data/gravel/BMC URS 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABD95D6-E0EA-B748-8B92-F2B893CDEBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B20BC4-A3EA-544D-901F-99A8BB7FC7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8920" yWindow="3160" windowWidth="19880" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -376,9 +376,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -398,17 +395,32 @@
   </si>
   <si>
     <t>https://us.bmc-switzerland.com/cdn/shop/files/bmc-2026-urs-one-gravel-bike-blue-1_1800x1800.jpg?v=1758296461</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Grenchen, Switzerland</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -431,8 +443,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -729,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -777,7 +790,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1437,26 +1450,26 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" t="s">
         <v>121</v>
-      </c>
-      <c r="B41" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1684,8 +1697,16 @@
       <c r="A77" t="s">
         <v>117</v>
       </c>
-      <c r="B77" t="s">
-        <v>118</v>
+      <c r="B77" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/BMC URS 2025.xlsx
+++ b/data/gravel/BMC URS 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B20BC4-A3EA-544D-901F-99A8BB7FC7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA2DC3F-C624-0E4A-BA3A-797BE1BFA1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8920" yWindow="3160" windowWidth="19880" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13160" yWindow="3880" windowWidth="19880" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -286,9 +286,6 @@
     <t>bottom_bracket</t>
   </si>
   <si>
-    <t>pf</t>
-  </si>
-  <si>
     <t>q_factor</t>
   </si>
   <si>
@@ -404,6 +401,12 @@
   </si>
   <si>
     <t>Grenchen, Switzerland</t>
+  </si>
+  <si>
+    <t>press fit</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1450,26 +1453,26 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
         <v>118</v>
-      </c>
-      <c r="B40" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
         <v>120</v>
-      </c>
-      <c r="B41" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" t="s">
         <v>122</v>
-      </c>
-      <c r="B42" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1533,82 +1536,94 @@
       <c r="A52" t="s">
         <v>85</v>
       </c>
+      <c r="B52">
+        <v>142</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>86</v>
       </c>
+      <c r="B53">
+        <v>100</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>87</v>
       </c>
-      <c r="B54" t="s">
-        <v>88</v>
+      <c r="B54" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" t="s">
         <v>91</v>
-      </c>
-      <c r="B57" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
         <v>95</v>
-      </c>
-      <c r="B60" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" t="s">
         <v>98</v>
-      </c>
-      <c r="B62" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
@@ -1616,7 +1631,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
         <v>75</v>
@@ -1624,31 +1639,31 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" t="s">
         <v>104</v>
-      </c>
-      <c r="B67" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>105</v>
+      </c>
+      <c r="B68" t="s">
         <v>106</v>
-      </c>
-      <c r="B68" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
         <v>75</v>
@@ -1656,7 +1671,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
@@ -1664,12 +1679,12 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B73" t="s">
         <v>75</v>
@@ -1677,36 +1692,36 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" t="s">
         <v>114</v>
-      </c>
-      <c r="B75" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" t="s">
         <v>126</v>
-      </c>
-      <c r="B78" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/BMC URS 2025.xlsx
+++ b/data/gravel/BMC URS 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA2DC3F-C624-0E4A-BA3A-797BE1BFA1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0DFF07-3E65-A746-B17C-2888D8E0D634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13160" yWindow="3880" windowWidth="19880" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8920" yWindow="3880" windowWidth="19880" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -407,6 +407,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -745,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1550,128 +1568,110 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>87</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>89</v>
-      </c>
-      <c r="B56">
-        <v>27.2</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>94</v>
-      </c>
-      <c r="B60" t="s">
-        <v>95</v>
+        <v>87</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="B62">
+        <v>27.2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="B63" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>103</v>
-      </c>
-      <c r="B67" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>107</v>
-      </c>
-      <c r="B69" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>108</v>
-      </c>
-      <c r="B70" t="s">
-        <v>75</v>
+        <v>100</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
@@ -1679,48 +1679,96 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>112</v>
+        <v>105</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>108</v>
+      </c>
+      <c r="B76" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>116</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
+      </c>
+      <c r="B77" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>125</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B84" t="s">
         <v>126</v>
       </c>
     </row>
